--- a/data/trans_dic/P80_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P80_R-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 1,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,07</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,29; 5,13</t>
+          <t>0,26; 3,42</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,45</t>
+          <t>0,47; 2,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,8</t>
+          <t>0,56; 2,44</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,15</t>
+          <t>1,66; 5,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,1; 4,05</t>
+          <t>0,96; 3,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,42</t>
+          <t>1,6; 4,03</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,23; 3,35</t>
+          <t>0,29; 3,59</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,62</t>
+          <t>0,34; 2,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,97</t>
+          <t>0,41; 2,1</t>
         </is>
       </c>
     </row>
@@ -754,7 +754,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -777,12 +777,12 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,81</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,74</t>
+          <t>0,3; 2,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,4</t>
+          <t>0,14; 1,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,29; 1,68</t>
+          <t>0,36; 1,73</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,13</t>
+          <t>2,06; 6,39</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 3,05</t>
+          <t>1,49; 3,85</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,84</t>
+          <t>2,08; 4,36</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,63%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,05</t>
+          <t>2,33; 5,11</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,63</t>
+          <t>0,99; 2,77</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,24; 3,01</t>
+          <t>1,9; 3,62</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 2,56</t>
+          <t>1,72; 2,97</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0,99; 1,73</t>
+          <t>1,17; 1,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,28; 1,98</t>
+          <t>1,52; 2,27</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>862</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1566</t>
+          <t>1088</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1735</t>
+          <t>1949</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 851</t>
+          <t>0; 4825</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 8879</t>
+          <t>0; 5373</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 9347</t>
+          <t>0; 6282</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>6981</t>
+          <t>6329</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6242</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>13223</t>
+          <t>12416</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1511; 26579</t>
+          <t>1376; 18162</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2775; 12599</t>
+          <t>2558; 12082</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6267; 28923</t>
+          <t>6078; 26206</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6942</t>
+          <t>9915</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7676</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14619</t>
+          <t>17480</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3220; 13126</t>
+          <t>5242; 18830</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3853; 14151</t>
+          <t>3437; 13640</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8845; 22742</t>
+          <t>10761; 27108</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3517</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4193</t>
+          <t>4387</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7710</t>
+          <t>8003</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>721; 10460</t>
+          <t>1081; 13407</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1346; 12482</t>
+          <t>1431; 11176</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3109; 15549</t>
+          <t>3249; 16700</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1408,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1696</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1483</t>
+          <t>1696</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5801</t>
+          <t>0; 6448</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5704</t>
+          <t>0; 7863</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>3121</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>4515</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>859; 7386</t>
+          <t>803; 6853</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>160; 3609</t>
+          <t>359; 4254</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1544; 8825</t>
+          <t>1923; 9232</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>21328</t>
+          <t>26869</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>15324</t>
+          <t>18510</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>36652</t>
+          <t>45379</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>11628; 38201</t>
+          <t>14840; 45941</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>5640; 25836</t>
+          <t>11454; 29625</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>21952; 56487</t>
+          <t>30895; 64803</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>23356</t>
+          <t>28524</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11549</t>
+          <t>14235</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>34905</t>
+          <t>42759</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>9599; 37587</t>
+          <t>18597; 40699</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5986; 18876</t>
+          <t>8224; 22995</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>20314; 49565</t>
+          <t>30868; 58972</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>65414</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>49148</t>
+          <t>55125</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>114562</t>
+          <t>134197</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>44958; 88555</t>
+          <t>60769; 104966</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>36004; 63275</t>
+          <t>43517; 70790</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>91253; 141103</t>
+          <t>110562; 164756</t>
         </is>
       </c>
     </row>
